--- a/data/trans_dic/P16A04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,47</t>
+          <t>0,82; 3,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,83</t>
+          <t>0,88; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,67</t>
+          <t>0,22; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,5</t>
+          <t>0,53; 5,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,01</t>
+          <t>0,66; 2,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,47</t>
+          <t>2,09; 5,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,5</t>
+          <t>1,23; 4,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,2</t>
+          <t>0,69; 5,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,67</t>
+          <t>0,98; 2,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,01</t>
+          <t>1,86; 4,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,51</t>
+          <t>0,92; 2,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,71</t>
+          <t>0,9; 4,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,85</t>
+          <t>0,4; 1,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,29</t>
+          <t>1,77; 4,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,83</t>
+          <t>2,01; 4,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,06</t>
+          <t>0,06; 3,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,09</t>
+          <t>1,56; 4,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,78</t>
+          <t>2,91; 6,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,1</t>
+          <t>1,48; 4,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,82</t>
+          <t>0,96; 3,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,45</t>
+          <t>1,15; 2,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,79</t>
+          <t>2,56; 4,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,0</t>
+          <t>2,06; 3,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,79</t>
+          <t>0,85; 2,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,71</t>
+          <t>0,29; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,68</t>
+          <t>1,28; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,64</t>
+          <t>1,34; 3,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,12</t>
+          <t>1,25; 4,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,57</t>
+          <t>1,14; 3,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,9</t>
+          <t>1,51; 4,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,66</t>
+          <t>1,28; 3,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,27</t>
+          <t>1,8; 4,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,28</t>
+          <t>0,83; 2,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,44</t>
+          <t>1,65; 3,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,07</t>
+          <t>1,45; 3,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,61</t>
+          <t>1,85; 3,68</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,31</t>
+          <t>0,73; 3,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,61</t>
+          <t>1,02; 3,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,34</t>
+          <t>0,97; 3,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,63</t>
+          <t>0,82; 3,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,85; 3,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,78</t>
+          <t>0,19; 1,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,07</t>
+          <t>2,24; 5,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,59</t>
+          <t>0,84; 2,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,73</t>
+          <t>1,08; 2,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,18</t>
+          <t>0,79; 2,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,96</t>
+          <t>1,64; 4,16</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,6</t>
+          <t>1,89; 5,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,99</t>
+          <t>1,59; 5,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,86</t>
+          <t>0,94; 3,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,17</t>
+          <t>1,5; 3,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,16</t>
+          <t>1,09; 4,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,59</t>
+          <t>0,92; 3,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,68</t>
+          <t>1,98; 5,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,27</t>
+          <t>2,78; 5,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,13</t>
+          <t>1,76; 4,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,91</t>
+          <t>1,55; 3,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,02</t>
+          <t>1,81; 4,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,13</t>
+          <t>2,41; 4,2</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,37</t>
+          <t>1,56; 5,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,11</t>
+          <t>3,05; 10,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,3</t>
+          <t>1,16; 5,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,06</t>
+          <t>1,41; 4,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,85</t>
+          <t>1,58; 4,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,71</t>
+          <t>1,33; 5,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,7</t>
+          <t>1,0; 4,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,79</t>
+          <t>0,63; 3,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,45</t>
+          <t>1,89; 4,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,3</t>
+          <t>2,52; 6,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,31</t>
+          <t>1,42; 4,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,43</t>
+          <t>1,22; 3,51</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,15</t>
+          <t>1,71; 7,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,96</t>
+          <t>1,81; 7,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,91</t>
+          <t>1,7; 5,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,03</t>
+          <t>1,56; 5,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,75</t>
+          <t>1,8; 5,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,83</t>
+          <t>1,25; 4,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,38</t>
+          <t>3,08; 6,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,4</t>
+          <t>2,07; 5,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,71</t>
+          <t>2,23; 5,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,35</t>
+          <t>0,97; 3,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,03</t>
+          <t>2,78; 5,03</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,28</t>
+          <t>1,38; 2,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,48</t>
+          <t>2,25; 3,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,59</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,82</t>
+          <t>1,56; 2,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,77</t>
+          <t>1,75; 2,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,52</t>
+          <t>2,28; 3,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,89</t>
+          <t>1,8; 2,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,73</t>
+          <t>2,49; 3,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,38</t>
+          <t>1,69; 2,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,29</t>
+          <t>2,43; 3,28</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,56</t>
+          <t>1,82; 2,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,08</t>
+          <t>2,17; 3,04</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4091; 17158</t>
+          <t>4067; 18424</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4610; 17347</t>
+          <t>3971; 16890</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>919; 6988</t>
+          <t>924; 7578</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2134; 21991</t>
+          <t>2130; 21421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3586; 14061</t>
+          <t>3077; 13941</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8886; 23466</t>
+          <t>8992; 23934</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4906; 17790</t>
+          <t>4863; 17446</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2199; 16296</t>
+          <t>2172; 17260</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10057; 25671</t>
+          <t>9426; 26674</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16319; 35356</t>
+          <t>16419; 35965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6747; 20443</t>
+          <t>7511; 20512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6954; 33566</t>
+          <t>6429; 30805</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2900; 13620</t>
+          <t>2942; 14065</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10978; 29452</t>
+          <t>12145; 30842</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11482; 28509</t>
+          <t>11841; 28913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168; 12953</t>
+          <t>267; 15120</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9588; 25555</t>
+          <t>9738; 25234</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18141; 41373</t>
+          <t>17755; 39821</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8235; 23093</t>
+          <t>8343; 22672</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5355; 19524</t>
+          <t>4915; 19813</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14704; 33277</t>
+          <t>15584; 34072</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33554; 62097</t>
+          <t>33193; 63245</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23163; 46181</t>
+          <t>23788; 45447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7415; 26126</t>
+          <t>7984; 25992</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1865; 10889</t>
+          <t>1872; 11126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9286; 24992</t>
+          <t>8709; 25210</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8215; 24342</t>
+          <t>8985; 25427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7356; 22109</t>
+          <t>6724; 22366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7739; 24616</t>
+          <t>7840; 24223</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10745; 27519</t>
+          <t>10675; 29840</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8179; 24229</t>
+          <t>8489; 24514</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9835; 23171</t>
+          <t>9745; 22684</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12004; 30248</t>
+          <t>11073; 28930</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23477; 47617</t>
+          <t>22817; 46457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18960; 40827</t>
+          <t>19271; 41038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19250; 38893</t>
+          <t>19955; 39691</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3732; 17206</t>
+          <t>3783; 16115</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6498; 22183</t>
+          <t>6296; 21285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6363; 21547</t>
+          <t>6286; 20660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7992; 32245</t>
+          <t>7309; 31889</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3027; 13859</t>
+          <t>3046; 13881</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4394; 17693</t>
+          <t>5247; 18828</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1957; 11562</t>
+          <t>1240; 11639</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15853; 43306</t>
+          <t>15964; 42614</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9769; 26758</t>
+          <t>8664; 24308</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12823; 33567</t>
+          <t>13316; 33243</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9912; 28195</t>
+          <t>10295; 28305</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24863; 63309</t>
+          <t>26265; 66641</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6911; 21656</t>
+          <t>7291; 22150</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6908; 21375</t>
+          <t>6810; 23010</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4756; 18435</t>
+          <t>4496; 18362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8125; 23360</t>
+          <t>8406; 22023</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4244; 16812</t>
+          <t>4384; 16708</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4143; 16063</t>
+          <t>4118; 16467</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10049; 28203</t>
+          <t>9860; 27693</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15228; 28700</t>
+          <t>15158; 28268</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14044; 32684</t>
+          <t>13944; 32215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12983; 34259</t>
+          <t>13541; 33240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17844; 39159</t>
+          <t>17605; 39018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26743; 45687</t>
+          <t>26586; 46388</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4612; 15722</t>
+          <t>4567; 15640</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9098; 31123</t>
+          <t>9386; 31815</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4219; 17704</t>
+          <t>3877; 18459</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5721; 14932</t>
+          <t>5195; 15763</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5063; 16636</t>
+          <t>5426; 16616</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4590; 16613</t>
+          <t>4697; 17729</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4351; 17748</t>
+          <t>3759; 18295</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4877; 23057</t>
+          <t>3856; 23421</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12067; 28254</t>
+          <t>12027; 28188</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16976; 41611</t>
+          <t>16640; 41738</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10423; 30696</t>
+          <t>10087; 28743</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11303; 33490</t>
+          <t>11888; 34269</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3605; 15001</t>
+          <t>3595; 15805</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4486; 19651</t>
+          <t>4469; 18125</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4990</t>
+          <t>0; 5803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4527; 13848</t>
+          <t>4790; 14215</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5522; 20144</t>
+          <t>5217; 19527</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7642; 22249</t>
+          <t>6981; 21517</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5034; 19323</t>
+          <t>4991; 19244</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13031; 27070</t>
+          <t>13062; 27245</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11103; 29349</t>
+          <t>11245; 29447</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14439; 36170</t>
+          <t>14151; 33846</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6065; 21996</t>
+          <t>6394; 22671</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19328; 35542</t>
+          <t>19649; 35554</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>45782; 74568</t>
+          <t>45311; 75059</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73191; 118752</t>
+          <t>76700; 118937</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53948; 87983</t>
+          <t>53214; 86710</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56889; 97638</t>
+          <t>54005; 97118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>58066; 93580</t>
+          <t>59272; 93543</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>83466; 124986</t>
+          <t>80717; 122792</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>63427; 102289</t>
+          <t>63836; 101231</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>88403; 136558</t>
+          <t>91030; 136067</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>112047; 158487</t>
+          <t>112191; 155307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>168636; 229140</t>
+          <t>168871; 228183</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>124314; 177422</t>
+          <t>126017; 177249</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>157336; 219395</t>
+          <t>154438; 216564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,73</t>
+          <t>0,82; 3,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,73</t>
+          <t>0,91; 3,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,81</t>
+          <t>0,22; 2,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,36</t>
+          <t>0,41; 5,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,98</t>
+          <t>0,64; 2,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,57</t>
+          <t>2,06; 5,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,41</t>
+          <t>1,23; 4,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,51</t>
+          <t>1,1; 5,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,77</t>
+          <t>0,99; 2,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,08</t>
+          <t>1,85; 3,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,52</t>
+          <t>0,85; 2,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,32</t>
+          <t>1,12; 4,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,91</t>
+          <t>0,4; 1,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,49</t>
+          <t>1,66; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,9</t>
+          <t>1,99; 5,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,57</t>
+          <t>0,29; 4,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,03</t>
+          <t>1,48; 4,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,53</t>
+          <t>2,95; 6,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,02</t>
+          <t>1,46; 4,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,87</t>
+          <t>1,4; 4,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,5</t>
+          <t>1,04; 2,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,88</t>
+          <t>2,64; 4,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,94</t>
+          <t>1,92; 3,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,78</t>
+          <t>1,03; 3,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,74</t>
+          <t>0,3; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,71</t>
+          <t>1,32; 3,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,8</t>
+          <t>1,27; 3,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,17</t>
+          <t>1,15; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,51</t>
+          <t>1,06; 3,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,23</t>
+          <t>1,57; 4,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,71</t>
+          <t>1,26; 3,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,18</t>
+          <t>1,84; 4,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,18</t>
+          <t>0,88; 2,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,36</t>
+          <t>1,72; 3,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,08</t>
+          <t>1,51; 3,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,68</t>
+          <t>1,77; 3,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,1</t>
+          <t>0,72; 3,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,46</t>
+          <t>0,87; 3,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,2</t>
+          <t>0,95; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,59</t>
+          <t>1,84; 4,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,69</t>
+          <t>0,59; 2,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,07</t>
+          <t>0,74; 2,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,79</t>
+          <t>0,3; 1,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,98</t>
+          <t>2,07; 3,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,35</t>
+          <t>0,87; 2,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,71</t>
+          <t>1,12; 2,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,19</t>
+          <t>0,78; 2,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,16</t>
+          <t>2,11; 3,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,73</t>
+          <t>1,77; 5,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,37</t>
+          <t>1,54; 5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,84</t>
+          <t>0,97; 3,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,93</t>
+          <t>1,46; 3,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,14</t>
+          <t>1,09; 4,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,68</t>
+          <t>0,92; 3,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,57</t>
+          <t>2,04; 5,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,19</t>
+          <t>3,11; 5,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,07</t>
+          <t>1,77; 4,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,79</t>
+          <t>1,49; 3,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,0</t>
+          <t>1,81; 4,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,2</t>
+          <t>2,65; 4,37</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,35</t>
+          <t>1,57; 5,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 10,34</t>
+          <t>3,11; 9,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,52</t>
+          <t>1,26; 4,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,28</t>
+          <t>1,33; 4,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,85</t>
+          <t>1,58; 5,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,02</t>
+          <t>1,32; 4,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,84</t>
+          <t>0,86; 4,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,85</t>
+          <t>2,35; 4,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,44</t>
+          <t>1,78; 4,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,32</t>
+          <t>2,58; 6,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,04</t>
+          <t>1,51; 4,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,51</t>
+          <t>2,2; 4,03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,53</t>
+          <t>1,82; 7,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,34</t>
+          <t>1,89; 7,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,04</t>
+          <t>1,73; 5,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,85</t>
+          <t>1,49; 5,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,56</t>
+          <t>1,72; 5,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,81</t>
+          <t>1,24; 4,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,42</t>
+          <t>3,31; 6,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,42</t>
+          <t>2,1; 5,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,34</t>
+          <t>2,25; 5,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,45</t>
+          <t>0,89; 3,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,03</t>
+          <t>2,89; 5,25</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,29</t>
+          <t>1,4; 2,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,48</t>
+          <t>2,28; 3,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,55</t>
+          <t>1,6; 2,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,81</t>
+          <t>1,81; 2,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,77</t>
+          <t>1,7; 2,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,46</t>
+          <t>2,37; 3,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,86</t>
+          <t>1,79; 2,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,72</t>
+          <t>2,82; 3,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,33</t>
+          <t>1,69; 2,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,28</t>
+          <t>2,43; 3,31</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,55</t>
+          <t>1,83; 2,59</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,04</t>
+          <t>2,51; 3,26</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>17177</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4067; 18424</t>
+          <t>4027; 16985</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3971; 16890</t>
+          <t>4105; 16406</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>924; 7578</t>
+          <t>924; 9372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2130; 21421</t>
+          <t>1679; 20459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3077; 13941</t>
+          <t>3015; 13156</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8992; 23934</t>
+          <t>8853; 24039</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4863; 17446</t>
+          <t>4881; 16863</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2172; 17260</t>
+          <t>3989; 19606</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9426; 26674</t>
+          <t>9567; 26016</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16419; 35965</t>
+          <t>16360; 35207</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7511; 20512</t>
+          <t>6940; 21832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6429; 30805</t>
+          <t>8641; 32659</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>18819</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2942; 14065</t>
+          <t>2906; 13873</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12145; 30842</t>
+          <t>11404; 29489</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11841; 28913</t>
+          <t>11772; 30012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>267; 15120</t>
+          <t>1377; 19222</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9738; 25234</t>
+          <t>9283; 25961</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17755; 39821</t>
+          <t>17983; 40457</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8343; 22672</t>
+          <t>8227; 24041</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4915; 19813</t>
+          <t>7015; 21642</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15584; 34072</t>
+          <t>14204; 33379</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33193; 63245</t>
+          <t>34206; 63860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23788; 45447</t>
+          <t>22138; 45001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7984; 25992</t>
+          <t>10112; 30618</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28332</t>
+          <t>31073</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1872; 11126</t>
+          <t>1889; 11284</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8709; 25210</t>
+          <t>8995; 25788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8985; 25427</t>
+          <t>8473; 24501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6724; 22366</t>
+          <t>7157; 22536</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7840; 24223</t>
+          <t>7280; 22177</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10675; 29840</t>
+          <t>11058; 28539</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8489; 24514</t>
+          <t>8305; 24009</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9745; 22684</t>
+          <t>11463; 26220</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11073; 28930</t>
+          <t>11707; 29349</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22817; 46457</t>
+          <t>23860; 47644</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19271; 41038</t>
+          <t>20026; 41631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19955; 39691</t>
+          <t>21946; 42045</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43252</t>
+          <t>42070</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3783; 16115</t>
+          <t>3744; 15981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6296; 21285</t>
+          <t>5324; 21752</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6286; 20660</t>
+          <t>6142; 20603</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7309; 31889</t>
+          <t>12867; 33859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3046; 13881</t>
+          <t>3054; 14574</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5247; 18828</t>
+          <t>4521; 18292</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1240; 11639</t>
+          <t>1980; 11627</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15964; 42614</t>
+          <t>15258; 29390</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8664; 24308</t>
+          <t>9043; 25443</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13316; 33243</t>
+          <t>13705; 33123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10295; 28305</t>
+          <t>10135; 27267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26265; 66641</t>
+          <t>30403; 56555</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>41124</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7291; 22150</t>
+          <t>6830; 21007</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6810; 23010</t>
+          <t>6594; 23404</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4496; 18362</t>
+          <t>4636; 17821</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8406; 22023</t>
+          <t>8853; 23114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4384; 16708</t>
+          <t>4418; 16815</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4118; 16467</t>
+          <t>4126; 15964</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9860; 27693</t>
+          <t>10132; 27461</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15158; 28268</t>
+          <t>18910; 33986</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13944; 32215</t>
+          <t>13984; 31743</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13541; 33240</t>
+          <t>13030; 33679</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17605; 39018</t>
+          <t>17642; 41062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26586; 46388</t>
+          <t>32234; 53170</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>25688</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4567; 15640</t>
+          <t>4605; 15374</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9386; 31815</t>
+          <t>9569; 30096</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3877; 18459</t>
+          <t>4213; 16608</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5195; 15763</t>
+          <t>5429; 16388</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5426; 16616</t>
+          <t>5412; 17811</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4697; 17729</t>
+          <t>4661; 17387</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3759; 18295</t>
+          <t>3233; 17593</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3856; 23421</t>
+          <t>10305; 21156</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12027; 28188</t>
+          <t>11336; 27855</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16640; 41738</t>
+          <t>17021; 41893</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10087; 28743</t>
+          <t>10759; 29388</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11888; 34269</t>
+          <t>18586; 34091</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>30340</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3595; 15805</t>
+          <t>3813; 15641</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4469; 18125</t>
+          <t>4655; 19401</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5803</t>
+          <t>0; 5008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4790; 14215</t>
+          <t>5348; 16635</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5217; 19527</t>
+          <t>4962; 19223</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6981; 21517</t>
+          <t>6658; 21090</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4991; 19244</t>
+          <t>4947; 19252</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13062; 27245</t>
+          <t>15317; 31175</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11245; 29447</t>
+          <t>11421; 30693</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14151; 33846</t>
+          <t>14266; 36604</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6394; 22671</t>
+          <t>5823; 20709</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19649; 35554</t>
+          <t>22355; 40592</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>124142</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>206290</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>45311; 75059</t>
+          <t>45808; 76703</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>76700; 118937</t>
+          <t>77743; 121968</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53214; 86710</t>
+          <t>54463; 88587</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54005; 97118</t>
+          <t>64087; 104513</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>59272; 93543</t>
+          <t>57529; 93713</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>80717; 122792</t>
+          <t>83879; 124616</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>63836; 101231</t>
+          <t>63356; 101368</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>91030; 136067</t>
+          <t>105311; 144065</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>112191; 155307</t>
+          <t>112708; 159284</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>168871; 228183</t>
+          <t>168997; 230362</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>126017; 177249</t>
+          <t>126736; 179493</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>154438; 216564</t>
+          <t>182214; 236764</t>
         </is>
       </c>
     </row>
